--- a/localcsms/web/admin-web/src/main/resources/RC_003.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_003.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2437AE6-3183-49C5-88B5-8A35BDFA9C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2233BE-6A77-484E-8741-B1E3F1D84673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2964" yWindow="6912" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>고객카드번호</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>충전금액(원)</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>충전소명</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -78,10 +74,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>${excelData.chUseCost}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>${excelData.paySum}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -114,10 +106,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>월간충전내역</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>단지명</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -159,6 +147,10 @@
   </si>
   <si>
     <t>${excelData.ho}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>월별충전내역</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -172,7 +164,7 @@
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -208,13 +200,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -295,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -341,9 +326,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -653,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:S5"/>
+  <dimension ref="B1:R5"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -668,34 +650,32 @@
     <col min="11" max="11" width="23" style="3" customWidth="1"/>
     <col min="12" max="12" width="15.5546875" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.44140625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16" style="2" customWidth="1"/>
-    <col min="15" max="17" width="16" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="9.21875" style="1"/>
+    <col min="14" max="16" width="16" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
+    <row r="1" spans="2:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
@@ -710,124 +690,117 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="2:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:19" ht="19.2" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>21</v>
+    <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:18" ht="19.2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="10" t="s">
+      <c r="R4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="8" t="s">
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="R5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="B1:R1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localcsms/web/admin-web/src/main/resources/RC_003.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_003.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2233BE-6A77-484E-8741-B1E3F1D84673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8268F0A7-C1E0-47E7-9AF5-6C2CE6CFE6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3276" yWindow="4752" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>고객카드번호</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -158,11 +158,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-* #,##0_р_._-;\-* #,##0_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="181" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -312,23 +313,23 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -635,64 +636,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:R5"/>
+  <dimension ref="B1:Q5"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
     <col min="3" max="4" width="28.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.21875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="4" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.21875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" style="2" customWidth="1"/>
-    <col min="14" max="16" width="16" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="23" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="2" customWidth="1"/>
+    <col min="13" max="15" width="16" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="2:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
+    <row r="2" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
     </row>
-    <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:18" ht="19.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:17" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
@@ -709,98 +709,92 @@
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="O4" s="6" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="11" t="s">
+      <c r="O5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="P5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="Q5" s="13" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="B1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
